--- a/moduli_aziende/aifecs/moduli_compilati/MOD-620-B-Pianificazione.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-620-B-Pianificazione.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78689ca3de2c44b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec10f1f849084f1f"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -378,12 +361,12 @@
         <x:v>Check</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="68" customHeight="1">
+    <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>Completezza fascicoli</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>Proposta: 100% fascicoli verificati completi prima del rilascio attestati.</x:v>
+        <x:v>100% fascicoli verificati completi prima del rilascio attestati.</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>Attestazione</x:v>
@@ -398,16 +381,14 @@
       <x:c r="G2" s="13" t="str">
         <x:f ca="1">IF(AND(ISNUMBER(F2),F2&gt;0),F2-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H2" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H2" s="10"/>
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="10" t="str">
         <x:v>Qualifica docenti</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>Proposta: 100% docenti incaricati con dossier verificato.</x:v>
+        <x:v>100% docenti incaricati con dossier verificato.</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
         <x:v>Docenza</x:v>
@@ -422,16 +403,14 @@
       <x:c r="G3" s="13" t="str">
         <x:f t="shared" ref="G3:G14" ca="1" si="0">IF(AND(ISNUMBER(F3),F3&gt;0),F3-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H3" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="68" customHeight="1">
+      <x:c r="H3" s="10"/>
+    </x:row>
+    <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="10" t="str">
         <x:v>Controllo centri</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Proposta: riesame annuale dei centri attivi secondo piano da approvare.</x:v>
+        <x:v>riesame annuale dei centri attivi secondo il piano annuale.</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
         <x:v>Gestione rete</x:v>
@@ -446,16 +425,14 @@
       <x:c r="G4" s="13" t="str">
         <x:f t="shared" ca="1" si="0">IF(AND(ISNUMBER(F4),F4&gt;0),F4-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H4" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H4" s="10"/>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
       <x:c r="A5" s="10" t="str">
         <x:v>Soddisfazione partecipanti</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>Proposta: media almeno 4/5; rilevare anche tasso di risposta.</x:v>
+        <x:v>media almeno 4/5; rilevare anche tasso di risposta.</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
         <x:v>Soddisfazione</x:v>
@@ -470,9 +447,7 @@
       <x:c r="G5" s="13" t="str">
         <x:f t="shared" ca="1" si="0">IF(AND(ISNUMBER(F5),F5&gt;0),F5-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H5" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H5" s="10"/>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="10" t="str">
@@ -494,9 +469,7 @@
       <x:c r="G6" s="13" t="str">
         <x:f t="shared" ca="1" si="0">IF(AND(ISNUMBER(F6),F6&gt;0),F6-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H6" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H6" s="10"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="10" t="str">
@@ -518,9 +491,7 @@
       <x:c r="G7" s="13" t="str">
         <x:f t="shared" ca="1" si="0">IF(AND(ISNUMBER(F7),F7&gt;0),F7-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H7" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H7" s="10"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="10" t="str">
@@ -542,9 +513,7 @@
       <x:c r="G8" s="13" t="str">
         <x:f t="shared" ca="1" si="0">IF(AND(ISNUMBER(F8),F8&gt;0),F8-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H8" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H8" s="10"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="10" t="str">
@@ -566,16 +535,14 @@
       <x:c r="G9" s="13" t="str">
         <x:f t="shared" ca="1" si="0">IF(AND(ISNUMBER(F9),F9&gt;0),F9-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H9" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H9" s="10"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="10" t="str">
         <x:v>Competenze interne</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>Proposta: attuare il piano approvato e verificare l’efficacia delle azioni prioritarie.</x:v>
+        <x:v>attuare il piano approvato e verificare l’efficacia delle azioni prioritarie.</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
         <x:v>Competenze</x:v>
@@ -590,9 +557,7 @@
       <x:c r="G10" s="13" t="str">
         <x:f t="shared" ca="1" si="0">IF(AND(ISNUMBER(F10),F10&gt;0),F10-TODAY(),"")</x:f>
       </x:c>
-      <x:c r="H10" s="10" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H10" s="10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
@@ -686,6 +651,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R827eef8ed4d1449a"/>
 </x:worksheet>
 </file>